--- a/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
+++ b/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -358,46 +358,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.指定文件，循环次数达到指定次数，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.指定文件，文件格式完全不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.指定文件，文件格式有部分一致，有部分不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.指定文件，循环次数达到指定次数之前，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.指定group，cs，cl，循环次数达到指定次数之前，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8.指定group,cs,cl，循环次数达到指定次数，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.指定文件，循环次数达到指定次数，记录比大于1%，退出，生成文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.指定文件，循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.指定group,cs,cl，循环次数达到指定次数，记录比大于1%，退出，生成文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.指定group,cs,cl，循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cl使用分区表，切分到两个组上，只检查一个组上的cl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -406,46 +366,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11.指定group,cs，（cs下有3个cl，其中两个cl在一个组上，一个cl切分到两个组上）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12.指定group,cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.指定cs,cl（cl切分到两个组上）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14.指定cs,cl（cl是主表，包含3个子表）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.指定group（包含3个cl，一个普通cl，一个切分的cl，一个主表）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.指定cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.指定的cs不存在（包含指定cs，cs和cl）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.指定的group不存在（包含指定group，group和cs，group和cl，group和cs和cl）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20.指定的cl不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>异常情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -467,6 +387,94 @@
   </si>
   <si>
     <t>丁普升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定文件，循环次数达到指定次数之前，记录比少于1%，退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定文件，循环次数达到指定次数，记录比少于1%，退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定文件，循环次数达到指定次数，记录比大于1%，退出，生成文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定文件，循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定文件，文件格式完全不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定文件，文件格式有部分一致，有部分不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group，cs，cl，循环次数达到指定次数之前，记录比少于1%，退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group,cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs,cl（cl切分到两个组上）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs,cl（cl是主表，包含3个子表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group（包含3个cl，一个普通cl，一个切分的cl，一个主表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定的group不存在（包含指定group，group和cs，group和cl，group和cs和cl）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定的cs不存在（包含指定cs，cs和cl）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定的cl不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group,cs,cl，循环次数达到指定次数1，记录比大于1%，退出，生成文件与报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group,cs，（cs下有3个cl，其中两个cl在一个组上，一个cl切分到两个组上）,循环次数达到指定次数，记录比少于1%，退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group,cs，（cs下有3个cl，其中两个cl在一个组上，一个cl切分到两个组上）,循环次数达到指定次数1，记录比大于1%，退出，生成文件与报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs,cl，循环次数达到指定次数1，记录比大于1%，退出，生成文件与报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数之前，记录比少于1%，退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比少于1%，退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比大于1%，退出，生成文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1290,127 +1298,127 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,228 +1926,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="89"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="86"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="90"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="86"/>
-      <c r="B6" s="93" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="58"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="90"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="58"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="90"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="90"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="86"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="90"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="86"/>
-      <c r="B10" s="63" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="90"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="60"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="91"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="54" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="89"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="81"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="63"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="74"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="75"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="81"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="69"/>
-      <c r="E20" s="70"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="86"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="66"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="74"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="75"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="82"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="64"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="83"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="90"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
     </row>
     <row r="28" spans="1:9" ht="40.5">
-      <c r="A28" s="61" t="s">
+      <c r="A28" s="70" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="42"/>
@@ -2166,7 +2174,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="61"/>
+      <c r="A29" s="70"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>61</v>
@@ -2181,7 +2189,7 @@
       <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="61"/>
+      <c r="A30" s="70"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43"/>
       <c r="D30" s="43" t="s">
@@ -2196,7 +2204,7 @@
       <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="61"/>
+      <c r="A31" s="70"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43"/>
       <c r="D31" s="43" t="s">
@@ -2213,7 +2221,7 @@
       <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="61"/>
+      <c r="A32" s="70"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43"/>
       <c r="D32" s="43" t="s">
@@ -2232,7 +2240,7 @@
       <c r="I32" s="43"/>
     </row>
     <row r="36" spans="1:12" ht="54">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="92" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="42"/>
@@ -2268,7 +2276,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A37" s="62"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="42"/>
       <c r="C37" s="43" t="s">
         <v>63</v>
@@ -2292,7 +2300,7 @@
       <c r="L37" s="43"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="62"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="42"/>
       <c r="C38" s="43" t="s">
         <v>63</v>
@@ -2316,7 +2324,7 @@
       <c r="L38" s="43"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="62"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>63</v>
@@ -2342,7 +2350,7 @@
       <c r="L39" s="43"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="62"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>63</v>
@@ -2370,7 +2378,7 @@
       <c r="L40" s="43"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="62"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>63</v>
@@ -2392,7 +2400,7 @@
       <c r="L41" s="43"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="62"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>63</v>
@@ -2414,7 +2422,7 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="62"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
         <v>63</v>
@@ -2438,7 +2446,7 @@
       <c r="L43" s="43"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="62"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>63</v>
@@ -2464,7 +2472,7 @@
       <c r="L44" s="43"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="62"/>
+      <c r="A45" s="92"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>63</v>
@@ -2486,7 +2494,7 @@
       <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="62"/>
+      <c r="A46" s="92"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43" t="s">
@@ -2508,7 +2516,7 @@
       <c r="L46" s="43"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="62"/>
+      <c r="A47" s="92"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43" t="s">
@@ -2530,7 +2538,7 @@
       <c r="L47" s="43"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="62"/>
+      <c r="A48" s="92"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43" t="s">
@@ -2554,7 +2562,7 @@
       <c r="L48" s="43"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="62"/>
+      <c r="A49" s="92"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43"/>
       <c r="D49" s="43" t="s">
@@ -2580,7 +2588,7 @@
       <c r="L49" s="43"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="62"/>
+      <c r="A50" s="92"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>63</v>
@@ -2600,7 +2608,7 @@
       <c r="L50" s="43"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="62"/>
+      <c r="A51" s="92"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>63</v>
@@ -2620,7 +2628,7 @@
       <c r="L51" s="43"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="62"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>63</v>
@@ -2642,7 +2650,7 @@
       <c r="L52" s="43"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="62"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43" t="s">
         <v>63</v>
@@ -2666,7 +2674,7 @@
       <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="62"/>
+      <c r="A54" s="92"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43" t="s">
@@ -2686,7 +2694,7 @@
       <c r="L54" s="43"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="62"/>
+      <c r="A55" s="92"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43" t="s">
@@ -2706,7 +2714,7 @@
       <c r="L55" s="43"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="62"/>
+      <c r="A56" s="92"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43"/>
       <c r="D56" s="43" t="s">
@@ -2728,7 +2736,7 @@
       <c r="L56" s="43"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="62"/>
+      <c r="A57" s="92"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43" t="s">
@@ -2752,7 +2760,7 @@
       <c r="L57" s="43"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="62"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="42"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
@@ -2770,7 +2778,7 @@
       <c r="L58" s="43"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="62"/>
+      <c r="A59" s="92"/>
       <c r="B59" s="42"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
@@ -2784,7 +2792,7 @@
       <c r="L59" s="43"/>
     </row>
     <row r="62" spans="1:12" ht="27">
-      <c r="A62" s="53" t="s">
+      <c r="A62" s="87" t="s">
         <v>74</v>
       </c>
       <c r="B62" s="42"/>
@@ -2801,7 +2809,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A63" s="53"/>
+      <c r="A63" s="87"/>
       <c r="B63" s="42" t="s">
         <v>75</v>
       </c>
@@ -2814,7 +2822,7 @@
       <c r="I63" s="43"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="53"/>
+      <c r="A64" s="87"/>
       <c r="B64" s="42" t="s">
         <v>76</v>
       </c>
@@ -2827,7 +2835,7 @@
       <c r="I64" s="43"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="53"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="42" t="s">
         <v>77</v>
       </c>
@@ -2840,7 +2848,7 @@
       <c r="I65" s="43"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="53"/>
+      <c r="A66" s="87"/>
       <c r="B66" s="42" t="s">
         <v>78</v>
       </c>
@@ -2853,7 +2861,7 @@
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="54"/>
+      <c r="A67" s="88"/>
       <c r="B67" s="42"/>
       <c r="C67" s="43"/>
       <c r="D67" s="43"/>
@@ -2864,8 +2872,8 @@
       <c r="I67" s="43"/>
     </row>
     <row r="70" spans="1:9" ht="27">
-      <c r="A70" s="53" t="s">
-        <v>105</v>
+      <c r="A70" s="87" t="s">
+        <v>85</v>
       </c>
       <c r="B70" s="42"/>
       <c r="C70" s="42"/>
@@ -2879,9 +2887,9 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="53"/>
+      <c r="A71" s="87"/>
       <c r="B71" s="42" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C71" s="43"/>
       <c r="D71" s="43"/>
@@ -2892,9 +2900,9 @@
       <c r="I71" s="43"/>
     </row>
     <row r="72" spans="1:9" ht="27">
-      <c r="A72" s="53"/>
+      <c r="A72" s="87"/>
       <c r="B72" s="42" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C72" s="43"/>
       <c r="D72" s="43"/>
@@ -2905,9 +2913,9 @@
       <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="53"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="42" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C73" s="43"/>
       <c r="D73" s="43"/>
@@ -2918,9 +2926,9 @@
       <c r="I73" s="43"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="53"/>
+      <c r="A74" s="87"/>
       <c r="B74" s="42" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C74" s="43"/>
       <c r="D74" s="43"/>
@@ -2931,7 +2939,7 @@
       <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="54"/>
+      <c r="A75" s="88"/>
       <c r="B75" s="42"/>
       <c r="C75" s="43"/>
       <c r="D75" s="43"/>
@@ -2943,6 +2951,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="G4:I5"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="G8:I9"/>
+    <mergeCell ref="G10:I11"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="A36:A59"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="C18:E18"/>
@@ -2959,27 +2988,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="G4:I5"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="G8:I9"/>
-    <mergeCell ref="G10:I11"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A36:A59"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3039,26 +3047,26 @@
         <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="79"/>
+      <c r="G4" s="53"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
         <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
+        <v>90</v>
+      </c>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3087,10 +3095,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO105"/>
+  <dimension ref="A1:AO113"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="52.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="72.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="1" customWidth="1"/>
     <col min="3" max="3" width="52.625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
@@ -3152,42 +3160,42 @@
     </row>
     <row r="3" spans="1:41">
       <c r="A3" s="26" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:41">
       <c r="A4" s="26" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
     </row>
     <row r="5" spans="1:41">
       <c r="A5" s="26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:41">
       <c r="A6" s="26" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" s="26" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:41">
       <c r="A8" s="26" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -3199,123 +3207,121 @@
     </row>
     <row r="10" spans="1:41">
       <c r="A10" s="26" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="26" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:41">
       <c r="A11" s="26" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
+      <c r="C11" s="26" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="12" spans="1:41">
-      <c r="A12" s="26" t="s">
-        <v>91</v>
-      </c>
+      <c r="A12" s="26"/>
       <c r="B12" s="26"/>
-      <c r="C12" s="26" t="s">
-        <v>94</v>
-      </c>
+      <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:41">
       <c r="A13" s="26" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:41">
-      <c r="A14" s="26"/>
+      <c r="A14" s="26" t="s">
+        <v>107</v>
+      </c>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:41">
-      <c r="A15" s="26" t="s">
-        <v>95</v>
-      </c>
+      <c r="A15" s="26"/>
       <c r="B15" s="26"/>
       <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:41">
       <c r="A16" s="26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B16" s="26"/>
       <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="26" t="s">
-        <v>97</v>
-      </c>
+      <c r="A17" s="26"/>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="26" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="26" t="s">
-        <v>101</v>
-      </c>
+      <c r="A21" s="26"/>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="26"/>
+      <c r="A22" s="26" t="s">
+        <v>101</v>
+      </c>
       <c r="B22" s="26"/>
       <c r="C22" s="26"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="26" t="s">
-        <v>103</v>
-      </c>
+      <c r="A23" s="26"/>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="26" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="26" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="26"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="26"/>
+      <c r="A26" s="26" t="s">
+        <v>111</v>
+      </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="26"/>
+      <c r="A27" s="26" t="s">
+        <v>112</v>
+      </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
     </row>
@@ -3325,7 +3331,9 @@
       <c r="C28" s="26"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="26"/>
+      <c r="A29" s="26" t="s">
+        <v>67</v>
+      </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
     </row>
@@ -3335,17 +3343,23 @@
       <c r="C30" s="26"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="26"/>
+      <c r="A31" s="26" t="s">
+        <v>102</v>
+      </c>
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="26"/>
+      <c r="A32" s="26" t="s">
+        <v>103</v>
+      </c>
       <c r="B32" s="26"/>
       <c r="C32" s="26"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="26"/>
+      <c r="A33" s="26" t="s">
+        <v>104</v>
+      </c>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
     </row>
@@ -3708,6 +3722,46 @@
       <c r="A105" s="26"/>
       <c r="B105" s="26"/>
       <c r="C105" s="26"/>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="26"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="26"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="26"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="26"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="26"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="26"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="26"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="26"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
+++ b/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="147">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -475,6 +475,115 @@
   </si>
   <si>
     <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10万数据测试时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100万数据测试时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000万数据测试时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1亿数据测试时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数不正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase2</t>
+  </si>
+  <si>
+    <t>testcase3</t>
+  </si>
+  <si>
+    <t>testcase4</t>
+  </si>
+  <si>
+    <t>testcase5</t>
+  </si>
+  <si>
+    <t>testcase6</t>
+  </si>
+  <si>
+    <t>testcase7</t>
+  </si>
+  <si>
+    <t>testcase8</t>
+  </si>
+  <si>
+    <t>testcase9</t>
+  </si>
+  <si>
+    <t>testcase10</t>
+  </si>
+  <si>
+    <t>testcase11</t>
+  </si>
+  <si>
+    <t>testcase12</t>
+  </si>
+  <si>
+    <t>testcase13</t>
+  </si>
+  <si>
+    <t>testcase14</t>
+  </si>
+  <si>
+    <t>testcase15</t>
+  </si>
+  <si>
+    <t>testcase16</t>
+  </si>
+  <si>
+    <t>testcase17</t>
+  </si>
+  <si>
+    <t>testcase18</t>
+  </si>
+  <si>
+    <t>testcase19</t>
+  </si>
+  <si>
+    <t>testcase20</t>
+  </si>
+  <si>
+    <t>testcase21</t>
+  </si>
+  <si>
+    <t>testcase22</t>
+  </si>
+  <si>
+    <t>testcase23</t>
+  </si>
+  <si>
+    <t>testcase24</t>
+  </si>
+  <si>
+    <t>testcase25</t>
+  </si>
+  <si>
+    <t>testcase26</t>
+  </si>
+  <si>
+    <t>testcase27</t>
+  </si>
+  <si>
+    <t>testcase28</t>
+  </si>
+  <si>
+    <t>参数不正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1298,127 +1407,127 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1926,228 +2035,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57" t="s">
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="89"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="61"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="90"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="61"/>
-      <c r="B6" s="75" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="90"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="90"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="58"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="90"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="61"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="90"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="61"/>
-      <c r="B10" s="74" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="90"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="91"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="60"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="80" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="57" t="s">
+      <c r="G18" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="89"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="55"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="74"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="63"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="75"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="55"/>
+      <c r="A20" s="81"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="86"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="55"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="76"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="74"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="63"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="56"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="83"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="68"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="90"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="93"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
     </row>
     <row r="28" spans="1:9" ht="40.5">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="61" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="42"/>
@@ -2174,7 +2283,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="70"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>61</v>
@@ -2189,7 +2298,7 @@
       <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="70"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43"/>
       <c r="D30" s="43" t="s">
@@ -2204,7 +2313,7 @@
       <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="70"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43"/>
       <c r="D31" s="43" t="s">
@@ -2221,7 +2330,7 @@
       <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="70"/>
+      <c r="A32" s="61"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43"/>
       <c r="D32" s="43" t="s">
@@ -2240,7 +2349,7 @@
       <c r="I32" s="43"/>
     </row>
     <row r="36" spans="1:12" ht="54">
-      <c r="A36" s="92" t="s">
+      <c r="A36" s="62" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="42"/>
@@ -2276,7 +2385,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A37" s="92"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="42"/>
       <c r="C37" s="43" t="s">
         <v>63</v>
@@ -2300,7 +2409,7 @@
       <c r="L37" s="43"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="92"/>
+      <c r="A38" s="62"/>
       <c r="B38" s="42"/>
       <c r="C38" s="43" t="s">
         <v>63</v>
@@ -2324,7 +2433,7 @@
       <c r="L38" s="43"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="92"/>
+      <c r="A39" s="62"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>63</v>
@@ -2350,7 +2459,7 @@
       <c r="L39" s="43"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="92"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>63</v>
@@ -2378,7 +2487,7 @@
       <c r="L40" s="43"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="92"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>63</v>
@@ -2400,7 +2509,7 @@
       <c r="L41" s="43"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="92"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>63</v>
@@ -2422,7 +2531,7 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="92"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
         <v>63</v>
@@ -2446,7 +2555,7 @@
       <c r="L43" s="43"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="92"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>63</v>
@@ -2472,7 +2581,7 @@
       <c r="L44" s="43"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="92"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>63</v>
@@ -2494,7 +2603,7 @@
       <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="92"/>
+      <c r="A46" s="62"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43" t="s">
@@ -2516,7 +2625,7 @@
       <c r="L46" s="43"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="92"/>
+      <c r="A47" s="62"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43" t="s">
@@ -2538,7 +2647,7 @@
       <c r="L47" s="43"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="92"/>
+      <c r="A48" s="62"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43" t="s">
@@ -2562,7 +2671,7 @@
       <c r="L48" s="43"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="92"/>
+      <c r="A49" s="62"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43"/>
       <c r="D49" s="43" t="s">
@@ -2588,7 +2697,7 @@
       <c r="L49" s="43"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="92"/>
+      <c r="A50" s="62"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>63</v>
@@ -2608,7 +2717,7 @@
       <c r="L50" s="43"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="92"/>
+      <c r="A51" s="62"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>63</v>
@@ -2628,7 +2737,7 @@
       <c r="L51" s="43"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="92"/>
+      <c r="A52" s="62"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>63</v>
@@ -2650,7 +2759,7 @@
       <c r="L52" s="43"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="92"/>
+      <c r="A53" s="62"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43" t="s">
         <v>63</v>
@@ -2674,7 +2783,7 @@
       <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="92"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43" t="s">
@@ -2694,7 +2803,7 @@
       <c r="L54" s="43"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="92"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43" t="s">
@@ -2714,7 +2823,7 @@
       <c r="L55" s="43"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="92"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43"/>
       <c r="D56" s="43" t="s">
@@ -2736,7 +2845,7 @@
       <c r="L56" s="43"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="92"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43" t="s">
@@ -2760,7 +2869,7 @@
       <c r="L57" s="43"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="92"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="42"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
@@ -2778,7 +2887,7 @@
       <c r="L58" s="43"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="92"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="42"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
@@ -2792,7 +2901,7 @@
       <c r="L59" s="43"/>
     </row>
     <row r="62" spans="1:12" ht="27">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="53" t="s">
         <v>74</v>
       </c>
       <c r="B62" s="42"/>
@@ -2809,7 +2918,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A63" s="87"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="42" t="s">
         <v>75</v>
       </c>
@@ -2822,7 +2931,7 @@
       <c r="I63" s="43"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="87"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="42" t="s">
         <v>76</v>
       </c>
@@ -2835,7 +2944,7 @@
       <c r="I64" s="43"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="87"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="42" t="s">
         <v>77</v>
       </c>
@@ -2848,7 +2957,7 @@
       <c r="I65" s="43"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="87"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="42" t="s">
         <v>78</v>
       </c>
@@ -2861,7 +2970,7 @@
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="88"/>
+      <c r="A67" s="54"/>
       <c r="B67" s="42"/>
       <c r="C67" s="43"/>
       <c r="D67" s="43"/>
@@ -2872,7 +2981,7 @@
       <c r="I67" s="43"/>
     </row>
     <row r="70" spans="1:9" ht="27">
-      <c r="A70" s="87" t="s">
+      <c r="A70" s="53" t="s">
         <v>85</v>
       </c>
       <c r="B70" s="42"/>
@@ -2887,7 +2996,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="87"/>
+      <c r="A71" s="53"/>
       <c r="B71" s="42" t="s">
         <v>86</v>
       </c>
@@ -2900,7 +3009,7 @@
       <c r="I71" s="43"/>
     </row>
     <row r="72" spans="1:9" ht="27">
-      <c r="A72" s="87"/>
+      <c r="A72" s="53"/>
       <c r="B72" s="42" t="s">
         <v>87</v>
       </c>
@@ -2913,7 +3022,7 @@
       <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="87"/>
+      <c r="A73" s="53"/>
       <c r="B73" s="42" t="s">
         <v>88</v>
       </c>
@@ -2926,7 +3035,7 @@
       <c r="I73" s="43"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="87"/>
+      <c r="A74" s="53"/>
       <c r="B74" s="42" t="s">
         <v>89</v>
       </c>
@@ -2939,8 +3048,10 @@
       <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="88"/>
-      <c r="B75" s="42"/>
+      <c r="A75" s="54"/>
+      <c r="B75" s="42" t="s">
+        <v>146</v>
+      </c>
       <c r="C75" s="43"/>
       <c r="D75" s="43"/>
       <c r="E75" s="43"/>
@@ -2951,6 +3062,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="C4:E5"/>
+    <mergeCell ref="C6:E7"/>
+    <mergeCell ref="C8:E9"/>
+    <mergeCell ref="C10:E11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A70:A75"/>
     <mergeCell ref="G4:I5"/>
@@ -2967,27 +3099,6 @@
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="G18:I18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="C4:E5"/>
-    <mergeCell ref="C6:E7"/>
-    <mergeCell ref="C8:E9"/>
-    <mergeCell ref="C10:E11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3049,10 +3160,10 @@
       <c r="C4" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="53"/>
+      <c r="G4" s="79"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
@@ -3061,12 +3172,12 @@
       <c r="C5" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3095,11 +3206,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO113"/>
+  <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="72.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="110.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="52.625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
@@ -3160,206 +3271,272 @@
     </row>
     <row r="3" spans="1:41">
       <c r="A3" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="26"/>
       <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:41">
       <c r="A4" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="26"/>
       <c r="C4" s="26"/>
     </row>
     <row r="5" spans="1:41">
       <c r="A5" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="26"/>
       <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:41">
       <c r="A6" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="26"/>
       <c r="C6" s="26"/>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:41">
       <c r="A8" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="26"/>
       <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:41">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
+      <c r="A9" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="10" spans="1:41">
       <c r="A10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="26"/>
+        <v>125</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>105</v>
+      </c>
       <c r="C10" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:41">
       <c r="A11" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26" t="s">
-        <v>84</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="26"/>
     </row>
     <row r="12" spans="1:41">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>107</v>
+      </c>
       <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:41">
       <c r="A13" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="26"/>
+        <v>128</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>98</v>
+      </c>
       <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:41">
       <c r="A14" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="26"/>
+        <v>129</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>99</v>
+      </c>
       <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:41">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>100</v>
+      </c>
       <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:41">
       <c r="A16" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="26"/>
+        <v>131</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>108</v>
+      </c>
       <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
+      <c r="A17" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>101</v>
+      </c>
       <c r="C17" s="26"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="26"/>
+        <v>133</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>109</v>
+      </c>
       <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="26"/>
+        <v>134</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>110</v>
+      </c>
       <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="26"/>
+        <v>135</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>111</v>
+      </c>
       <c r="C20" s="26"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
+      <c r="A21" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>112</v>
+      </c>
       <c r="C21" s="26"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="26"/>
+        <v>137</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>67</v>
+      </c>
       <c r="C22" s="26"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
+      <c r="A23" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>102</v>
+      </c>
       <c r="C23" s="26"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="26"/>
+        <v>139</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>103</v>
+      </c>
       <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="26"/>
+        <v>140</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>104</v>
+      </c>
       <c r="C25" s="26"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="26"/>
+        <v>141</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>113</v>
+      </c>
       <c r="C26" s="26"/>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="26"/>
+        <v>142</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>114</v>
+      </c>
       <c r="C27" s="26"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="26"/>
+      <c r="A28" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="C28" s="26"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="26"/>
+        <v>144</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>116</v>
+      </c>
       <c r="C29" s="26"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
+      <c r="A30" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>117</v>
+      </c>
       <c r="C30" s="26"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="26" t="s">
-        <v>102</v>
-      </c>
+      <c r="A31" s="26"/>
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="26" t="s">
-        <v>103</v>
-      </c>
+      <c r="A32" s="26"/>
       <c r="B32" s="26"/>
       <c r="C32" s="26"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="26" t="s">
-        <v>104</v>
-      </c>
+      <c r="A33" s="26"/>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
     </row>
@@ -3722,46 +3899,6 @@
       <c r="A105" s="26"/>
       <c r="B105" s="26"/>
       <c r="C105" s="26"/>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="26"/>
-      <c r="B106" s="26"/>
-      <c r="C106" s="26"/>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="26"/>
-      <c r="B107" s="26"/>
-      <c r="C107" s="26"/>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="26"/>
-      <c r="B108" s="26"/>
-      <c r="C108" s="26"/>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="26"/>
-      <c r="B109" s="26"/>
-      <c r="C109" s="26"/>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="26"/>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="26"/>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="26"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="26"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
+++ b/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="9150" windowHeight="3705" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="122">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -358,14 +358,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cl使用分区表，切分到两个组上，只检查一个组上的cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cl使用主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>异常情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -394,14 +386,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指定文件，循环次数达到指定次数，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定文件，循环次数达到指定次数，记录比大于1%，退出，生成文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指定文件，循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -410,30 +394,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指定文件，文件格式有部分一致，有部分不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定group，cs，cl，循环次数达到指定次数之前，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指定group,cl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指定cs,cl（cl切分到两个组上）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定cs,cl（cl是主表，包含3个子表）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定group（包含3个cl，一个普通cl，一个切分的cl，一个主表）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指定的group不存在（包含指定group，group和cs，group和cl，group和cs和cl）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -442,42 +406,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指定的cl不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指定group,cs,cl，循环次数达到指定次数1，记录比大于1%，退出，生成文件与报告</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指定group,cs，（cs下有3个cl，其中两个cl在一个组上，一个cl切分到两个组上）,循环次数达到指定次数，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定group,cs，（cs下有3个cl，其中两个cl在一个组上，一个cl切分到两个组上）,循环次数达到指定次数1，记录比大于1%，退出，生成文件与报告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定cs,cl，循环次数达到指定次数1，记录比大于1%，退出，生成文件与报告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数之前，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比少于1%，退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比大于1%，退出，生成文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定cs（cs下有3个cl，一个普通cl，一个切分cl，一个主表）循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10万数据测试时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -490,10 +422,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1亿数据测试时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>参数不正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -547,43 +475,27 @@
     <t>testcase16</t>
   </si>
   <si>
+    <t>参数不正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs,cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定group,cs，（cs下有4个cl，其中两个cl为子表，一个为主表，一个cl为普通cl）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs，循环次数达到指定次数，记录比大于1%，退出，生成文件与报告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>testcase17</t>
-  </si>
-  <si>
-    <t>testcase18</t>
-  </si>
-  <si>
-    <t>testcase19</t>
-  </si>
-  <si>
-    <t>testcase20</t>
-  </si>
-  <si>
-    <t>testcase21</t>
-  </si>
-  <si>
-    <t>testcase22</t>
-  </si>
-  <si>
-    <t>testcase23</t>
-  </si>
-  <si>
-    <t>testcase24</t>
-  </si>
-  <si>
-    <t>testcase25</t>
-  </si>
-  <si>
-    <t>testcase26</t>
-  </si>
-  <si>
-    <t>testcase27</t>
-  </si>
-  <si>
-    <t>testcase28</t>
-  </si>
-  <si>
-    <t>参数不正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定cs,cl （cl 为主表）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1407,127 +1319,127 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2035,228 +1947,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="89"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="86"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="90"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="86"/>
-      <c r="B6" s="93" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="58"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="90"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="58"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="90"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="90"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="86"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="90"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="86"/>
-      <c r="B10" s="63" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="90"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="60"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="91"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="54" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="89"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="81"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="63"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="74"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="75"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="81"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="86"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="74"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="75"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="82"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="64"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="83"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="90"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
     </row>
     <row r="28" spans="1:9" ht="40.5">
-      <c r="A28" s="61" t="s">
+      <c r="A28" s="70" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="42"/>
@@ -2283,7 +2195,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="61"/>
+      <c r="A29" s="70"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>61</v>
@@ -2298,7 +2210,7 @@
       <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="61"/>
+      <c r="A30" s="70"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43"/>
       <c r="D30" s="43" t="s">
@@ -2313,7 +2225,7 @@
       <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="61"/>
+      <c r="A31" s="70"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43"/>
       <c r="D31" s="43" t="s">
@@ -2330,7 +2242,7 @@
       <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="61"/>
+      <c r="A32" s="70"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43"/>
       <c r="D32" s="43" t="s">
@@ -2349,7 +2261,7 @@
       <c r="I32" s="43"/>
     </row>
     <row r="36" spans="1:12" ht="54">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="92" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="42"/>
@@ -2385,7 +2297,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A37" s="62"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="42"/>
       <c r="C37" s="43" t="s">
         <v>63</v>
@@ -2409,7 +2321,7 @@
       <c r="L37" s="43"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="62"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="42"/>
       <c r="C38" s="43" t="s">
         <v>63</v>
@@ -2433,7 +2345,7 @@
       <c r="L38" s="43"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="62"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>63</v>
@@ -2459,7 +2371,7 @@
       <c r="L39" s="43"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="62"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>63</v>
@@ -2487,7 +2399,7 @@
       <c r="L40" s="43"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="62"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>63</v>
@@ -2509,7 +2421,7 @@
       <c r="L41" s="43"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="62"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>63</v>
@@ -2531,7 +2443,7 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="62"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
         <v>63</v>
@@ -2555,7 +2467,7 @@
       <c r="L43" s="43"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="62"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>63</v>
@@ -2581,7 +2493,7 @@
       <c r="L44" s="43"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="62"/>
+      <c r="A45" s="92"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>63</v>
@@ -2603,7 +2515,7 @@
       <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="62"/>
+      <c r="A46" s="92"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43" t="s">
@@ -2625,7 +2537,7 @@
       <c r="L46" s="43"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="62"/>
+      <c r="A47" s="92"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43" t="s">
@@ -2647,7 +2559,7 @@
       <c r="L47" s="43"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="62"/>
+      <c r="A48" s="92"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43" t="s">
@@ -2671,7 +2583,7 @@
       <c r="L48" s="43"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="62"/>
+      <c r="A49" s="92"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43"/>
       <c r="D49" s="43" t="s">
@@ -2697,7 +2609,7 @@
       <c r="L49" s="43"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="62"/>
+      <c r="A50" s="92"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>63</v>
@@ -2717,7 +2629,7 @@
       <c r="L50" s="43"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="62"/>
+      <c r="A51" s="92"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>63</v>
@@ -2737,7 +2649,7 @@
       <c r="L51" s="43"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="62"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>63</v>
@@ -2759,7 +2671,7 @@
       <c r="L52" s="43"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="62"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43" t="s">
         <v>63</v>
@@ -2783,7 +2695,7 @@
       <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="62"/>
+      <c r="A54" s="92"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43" t="s">
@@ -2803,7 +2715,7 @@
       <c r="L54" s="43"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="62"/>
+      <c r="A55" s="92"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43" t="s">
@@ -2823,7 +2735,7 @@
       <c r="L55" s="43"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="62"/>
+      <c r="A56" s="92"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43"/>
       <c r="D56" s="43" t="s">
@@ -2845,7 +2757,7 @@
       <c r="L56" s="43"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="62"/>
+      <c r="A57" s="92"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43" t="s">
@@ -2869,7 +2781,7 @@
       <c r="L57" s="43"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="62"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="42"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
@@ -2887,7 +2799,7 @@
       <c r="L58" s="43"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="62"/>
+      <c r="A59" s="92"/>
       <c r="B59" s="42"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
@@ -2901,7 +2813,7 @@
       <c r="L59" s="43"/>
     </row>
     <row r="62" spans="1:12" ht="27">
-      <c r="A62" s="53" t="s">
+      <c r="A62" s="87" t="s">
         <v>74</v>
       </c>
       <c r="B62" s="42"/>
@@ -2918,7 +2830,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A63" s="53"/>
+      <c r="A63" s="87"/>
       <c r="B63" s="42" t="s">
         <v>75</v>
       </c>
@@ -2931,7 +2843,7 @@
       <c r="I63" s="43"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="53"/>
+      <c r="A64" s="87"/>
       <c r="B64" s="42" t="s">
         <v>76</v>
       </c>
@@ -2944,7 +2856,7 @@
       <c r="I64" s="43"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="53"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="42" t="s">
         <v>77</v>
       </c>
@@ -2957,7 +2869,7 @@
       <c r="I65" s="43"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="53"/>
+      <c r="A66" s="87"/>
       <c r="B66" s="42" t="s">
         <v>78</v>
       </c>
@@ -2970,7 +2882,7 @@
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="54"/>
+      <c r="A67" s="88"/>
       <c r="B67" s="42"/>
       <c r="C67" s="43"/>
       <c r="D67" s="43"/>
@@ -2981,8 +2893,8 @@
       <c r="I67" s="43"/>
     </row>
     <row r="70" spans="1:9" ht="27">
-      <c r="A70" s="53" t="s">
-        <v>85</v>
+      <c r="A70" s="87" t="s">
+        <v>83</v>
       </c>
       <c r="B70" s="42"/>
       <c r="C70" s="42"/>
@@ -2996,9 +2908,9 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="53"/>
+      <c r="A71" s="87"/>
       <c r="B71" s="42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C71" s="43"/>
       <c r="D71" s="43"/>
@@ -3009,9 +2921,9 @@
       <c r="I71" s="43"/>
     </row>
     <row r="72" spans="1:9" ht="27">
-      <c r="A72" s="53"/>
+      <c r="A72" s="87"/>
       <c r="B72" s="42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C72" s="43"/>
       <c r="D72" s="43"/>
@@ -3022,9 +2934,9 @@
       <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="53"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C73" s="43"/>
       <c r="D73" s="43"/>
@@ -3035,9 +2947,9 @@
       <c r="I73" s="43"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="53"/>
+      <c r="A74" s="87"/>
       <c r="B74" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C74" s="43"/>
       <c r="D74" s="43"/>
@@ -3048,9 +2960,9 @@
       <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="54"/>
+      <c r="A75" s="88"/>
       <c r="B75" s="42" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C75" s="43"/>
       <c r="D75" s="43"/>
@@ -3062,6 +2974,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="G4:I5"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="G8:I9"/>
+    <mergeCell ref="G10:I11"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="A36:A59"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="C18:E18"/>
@@ -3078,27 +3011,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="G4:I5"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="G8:I9"/>
-    <mergeCell ref="G10:I11"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A36:A59"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3158,26 +3070,26 @@
         <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="79"/>
+      <c r="G4" s="53"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
         <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
+        <v>88</v>
+      </c>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3206,11 +3118,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO105"/>
+  <dimension ref="A1:AO93"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="110.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="84.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="52.625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
@@ -3271,258 +3183,210 @@
     </row>
     <row r="3" spans="1:41">
       <c r="A3" s="26" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:41">
       <c r="A4" s="26" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" s="26"/>
     </row>
     <row r="5" spans="1:41">
       <c r="A5" s="26" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:41">
       <c r="A6" s="26" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C6" s="26"/>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" s="26" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:41">
       <c r="A8" s="26" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:41">
       <c r="A9" s="26" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>83</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C9" s="26"/>
     </row>
     <row r="10" spans="1:41">
       <c r="A10" s="26" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>84</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:41">
       <c r="A11" s="26" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C11" s="26"/>
     </row>
     <row r="12" spans="1:41">
       <c r="A12" s="26" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:41">
       <c r="A13" s="26" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:41">
       <c r="A14" s="26" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:41">
       <c r="A15" s="26" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:41">
       <c r="A16" s="26" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="26" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C17" s="26"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="26" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C18" s="26"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="26" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>111</v>
-      </c>
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="26"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>112</v>
-      </c>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="26"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>67</v>
-      </c>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="26"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>102</v>
-      </c>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="26"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>103</v>
-      </c>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>104</v>
-      </c>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="26"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>113</v>
-      </c>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="26"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>114</v>
-      </c>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="26"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>115</v>
-      </c>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="26"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>116</v>
-      </c>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="26"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>117</v>
-      </c>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="26"/>
     </row>
     <row r="31" spans="1:3">
@@ -3840,69 +3704,10 @@
       <c r="B93" s="26"/>
       <c r="C93" s="26"/>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="26"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="26"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="26"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26"/>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="26"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="26"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="26"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="26"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="26"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="26"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="26"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="26"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="26"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
+++ b/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="9150" windowHeight="3705" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="9150" windowHeight="3705" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="129">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -496,6 +496,37 @@
   </si>
   <si>
     <t>指定cs,cl （cl 为主表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该工具基本实现了story中的需求，能够正确的检测出集群中不一致的数据，真正实现了数据的一致性校验，在对大数据量的集群数据进行检测时，工具开销的时间能处于用户接受的范围之内。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具实现了集群数据一致性校验的目标。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.bug jira单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.自动化测试用例，已提交到SVN目录 4-testcase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. [sdbInspect工具]输入一个存在的cs，不存在的cl时，生成报告并显示没有不同记录，集群数据已完成同步，这是有问题的。http://jira:8080/browse/SEQUOIADBMAINSTREAM-294
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2.[sdbInspect工具]指定检查一个cs下的所有集合时，实际上会去检查所有的cs下的所有集合                        http://jira:8080/browse/SEQUOIADBMAINSTREAM-302
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3. [sdbInspect] 指定检查一个主表时，没有检查出子表的不同数据记录                                        http://jira:8080/browse/SEQUOIADBMAINSTREAM-303
+                       </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1319,127 +1350,127 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1947,228 +1978,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57" t="s">
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="89"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="61"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="90"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="61"/>
-      <c r="B6" s="75" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="90"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="90"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="58"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="90"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="61"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="90"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="61"/>
-      <c r="B10" s="74" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="90"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="91"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="60"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="80" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="57" t="s">
+      <c r="G18" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="89"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="55"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="74"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="63"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="75"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="55"/>
+      <c r="A20" s="81"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="86"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="55"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="76"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="74"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="63"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="56"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="83"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="68"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="90"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="93"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
     </row>
     <row r="28" spans="1:9" ht="40.5">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="61" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="42"/>
@@ -2195,7 +2226,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="70"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>61</v>
@@ -2210,7 +2241,7 @@
       <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="70"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43"/>
       <c r="D30" s="43" t="s">
@@ -2225,7 +2256,7 @@
       <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="70"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43"/>
       <c r="D31" s="43" t="s">
@@ -2242,7 +2273,7 @@
       <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="70"/>
+      <c r="A32" s="61"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43"/>
       <c r="D32" s="43" t="s">
@@ -2261,7 +2292,7 @@
       <c r="I32" s="43"/>
     </row>
     <row r="36" spans="1:12" ht="54">
-      <c r="A36" s="92" t="s">
+      <c r="A36" s="62" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="42"/>
@@ -2297,7 +2328,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A37" s="92"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="42"/>
       <c r="C37" s="43" t="s">
         <v>63</v>
@@ -2321,7 +2352,7 @@
       <c r="L37" s="43"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="92"/>
+      <c r="A38" s="62"/>
       <c r="B38" s="42"/>
       <c r="C38" s="43" t="s">
         <v>63</v>
@@ -2345,7 +2376,7 @@
       <c r="L38" s="43"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="92"/>
+      <c r="A39" s="62"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>63</v>
@@ -2371,7 +2402,7 @@
       <c r="L39" s="43"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="92"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>63</v>
@@ -2399,7 +2430,7 @@
       <c r="L40" s="43"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="92"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>63</v>
@@ -2421,7 +2452,7 @@
       <c r="L41" s="43"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="92"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>63</v>
@@ -2443,7 +2474,7 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="92"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
         <v>63</v>
@@ -2467,7 +2498,7 @@
       <c r="L43" s="43"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="92"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>63</v>
@@ -2493,7 +2524,7 @@
       <c r="L44" s="43"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="92"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>63</v>
@@ -2515,7 +2546,7 @@
       <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="92"/>
+      <c r="A46" s="62"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43" t="s">
@@ -2537,7 +2568,7 @@
       <c r="L46" s="43"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="92"/>
+      <c r="A47" s="62"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43" t="s">
@@ -2559,7 +2590,7 @@
       <c r="L47" s="43"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="92"/>
+      <c r="A48" s="62"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43" t="s">
@@ -2583,7 +2614,7 @@
       <c r="L48" s="43"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="92"/>
+      <c r="A49" s="62"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43"/>
       <c r="D49" s="43" t="s">
@@ -2609,7 +2640,7 @@
       <c r="L49" s="43"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="92"/>
+      <c r="A50" s="62"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>63</v>
@@ -2629,7 +2660,7 @@
       <c r="L50" s="43"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="92"/>
+      <c r="A51" s="62"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>63</v>
@@ -2649,7 +2680,7 @@
       <c r="L51" s="43"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="92"/>
+      <c r="A52" s="62"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>63</v>
@@ -2671,7 +2702,7 @@
       <c r="L52" s="43"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="92"/>
+      <c r="A53" s="62"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43" t="s">
         <v>63</v>
@@ -2695,7 +2726,7 @@
       <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="92"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43" t="s">
@@ -2715,7 +2746,7 @@
       <c r="L54" s="43"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="92"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43" t="s">
@@ -2735,7 +2766,7 @@
       <c r="L55" s="43"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="92"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43"/>
       <c r="D56" s="43" t="s">
@@ -2757,7 +2788,7 @@
       <c r="L56" s="43"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="92"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43" t="s">
@@ -2781,7 +2812,7 @@
       <c r="L57" s="43"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="92"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="42"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
@@ -2799,7 +2830,7 @@
       <c r="L58" s="43"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="92"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="42"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
@@ -2813,7 +2844,7 @@
       <c r="L59" s="43"/>
     </row>
     <row r="62" spans="1:12" ht="27">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="53" t="s">
         <v>74</v>
       </c>
       <c r="B62" s="42"/>
@@ -2830,7 +2861,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A63" s="87"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="42" t="s">
         <v>75</v>
       </c>
@@ -2843,7 +2874,7 @@
       <c r="I63" s="43"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="87"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="42" t="s">
         <v>76</v>
       </c>
@@ -2856,7 +2887,7 @@
       <c r="I64" s="43"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="87"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="42" t="s">
         <v>77</v>
       </c>
@@ -2869,7 +2900,7 @@
       <c r="I65" s="43"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="87"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="42" t="s">
         <v>78</v>
       </c>
@@ -2882,7 +2913,7 @@
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="88"/>
+      <c r="A67" s="54"/>
       <c r="B67" s="42"/>
       <c r="C67" s="43"/>
       <c r="D67" s="43"/>
@@ -2893,7 +2924,7 @@
       <c r="I67" s="43"/>
     </row>
     <row r="70" spans="1:9" ht="27">
-      <c r="A70" s="87" t="s">
+      <c r="A70" s="53" t="s">
         <v>83</v>
       </c>
       <c r="B70" s="42"/>
@@ -2908,7 +2939,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="87"/>
+      <c r="A71" s="53"/>
       <c r="B71" s="42" t="s">
         <v>84</v>
       </c>
@@ -2921,7 +2952,7 @@
       <c r="I71" s="43"/>
     </row>
     <row r="72" spans="1:9" ht="27">
-      <c r="A72" s="87"/>
+      <c r="A72" s="53"/>
       <c r="B72" s="42" t="s">
         <v>85</v>
       </c>
@@ -2934,7 +2965,7 @@
       <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="87"/>
+      <c r="A73" s="53"/>
       <c r="B73" s="42" t="s">
         <v>86</v>
       </c>
@@ -2947,7 +2978,7 @@
       <c r="I73" s="43"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="87"/>
+      <c r="A74" s="53"/>
       <c r="B74" s="42" t="s">
         <v>87</v>
       </c>
@@ -2960,7 +2991,7 @@
       <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="88"/>
+      <c r="A75" s="54"/>
       <c r="B75" s="42" t="s">
         <v>116</v>
       </c>
@@ -2974,6 +3005,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="C4:E5"/>
+    <mergeCell ref="C6:E7"/>
+    <mergeCell ref="C8:E9"/>
+    <mergeCell ref="C10:E11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A70:A75"/>
     <mergeCell ref="G4:I5"/>
@@ -2990,27 +3042,6 @@
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="G18:I18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="C4:E5"/>
-    <mergeCell ref="C6:E7"/>
-    <mergeCell ref="C8:E9"/>
-    <mergeCell ref="C10:E11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3072,10 +3103,10 @@
       <c r="C4" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="53"/>
+      <c r="G4" s="79"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
@@ -3084,12 +3115,12 @@
       <c r="C5" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3740,6 +3771,11 @@
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>122</v>
+      </c>
+    </row>
     <row r="7" spans="1:7">
       <c r="A7" s="23" t="s">
         <v>45</v>
@@ -3751,6 +3787,11 @@
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
     </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="15" spans="1:7">
       <c r="A15" s="23" t="s">
         <v>47</v>
@@ -3761,6 +3802,16 @@
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="23" t="s">
@@ -3782,11 +3833,31 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="138.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="40.5">
+      <c r="A1" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="40.5">
+      <c r="A2" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="40.5">
+      <c r="A3" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
+++ b/testprocess/1-process/数据一致性校验工具/数据一致性校验.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="137">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -503,10 +503,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工具实现了集群数据一致性校验的目标。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2.bug jira单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -527,6 +523,42 @@
   <si>
     <t xml:space="preserve">3. [sdbInspect] 指定检查一个主表时，没有检查出子表的不同数据记录                                        http://jira:8080/browse/SEQUOIADBMAINSTREAM-303
                        </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33s左右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.5s左右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4s左右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有专门的自动化测试用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具实现了集群数据一致性校验的目标，可供用户正常使用。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,7 +566,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,6 +635,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -648,7 +688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -1204,11 +1244,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1350,127 +1403,127 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,6 +1531,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1978,228 +2039,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="89"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="86"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="90"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="86"/>
-      <c r="B6" s="93" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="58"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="90"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="58"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="90"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="90"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="86"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="90"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="86"/>
-      <c r="B10" s="63" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="90"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="60"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="91"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="54" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="89"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="81"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="63"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="74"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="75"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="81"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="86"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="74"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="75"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="82"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="64"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="83"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="90"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
     </row>
     <row r="28" spans="1:9" ht="40.5">
-      <c r="A28" s="61" t="s">
+      <c r="A28" s="70" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="42"/>
@@ -2226,7 +2287,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="61"/>
+      <c r="A29" s="70"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>61</v>
@@ -2241,7 +2302,7 @@
       <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="61"/>
+      <c r="A30" s="70"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43"/>
       <c r="D30" s="43" t="s">
@@ -2256,7 +2317,7 @@
       <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="61"/>
+      <c r="A31" s="70"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43"/>
       <c r="D31" s="43" t="s">
@@ -2273,7 +2334,7 @@
       <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="61"/>
+      <c r="A32" s="70"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43"/>
       <c r="D32" s="43" t="s">
@@ -2292,7 +2353,7 @@
       <c r="I32" s="43"/>
     </row>
     <row r="36" spans="1:12" ht="54">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="92" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="42"/>
@@ -2328,7 +2389,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A37" s="62"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="42"/>
       <c r="C37" s="43" t="s">
         <v>63</v>
@@ -2352,7 +2413,7 @@
       <c r="L37" s="43"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="62"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="42"/>
       <c r="C38" s="43" t="s">
         <v>63</v>
@@ -2376,7 +2437,7 @@
       <c r="L38" s="43"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="62"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>63</v>
@@ -2402,7 +2463,7 @@
       <c r="L39" s="43"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="62"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>63</v>
@@ -2430,7 +2491,7 @@
       <c r="L40" s="43"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="62"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>63</v>
@@ -2452,7 +2513,7 @@
       <c r="L41" s="43"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="62"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>63</v>
@@ -2474,7 +2535,7 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="62"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
         <v>63</v>
@@ -2498,7 +2559,7 @@
       <c r="L43" s="43"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="62"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>63</v>
@@ -2524,7 +2585,7 @@
       <c r="L44" s="43"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="62"/>
+      <c r="A45" s="92"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>63</v>
@@ -2546,7 +2607,7 @@
       <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="62"/>
+      <c r="A46" s="92"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43" t="s">
@@ -2568,7 +2629,7 @@
       <c r="L46" s="43"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="62"/>
+      <c r="A47" s="92"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43" t="s">
@@ -2590,7 +2651,7 @@
       <c r="L47" s="43"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="62"/>
+      <c r="A48" s="92"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43" t="s">
@@ -2614,7 +2675,7 @@
       <c r="L48" s="43"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="62"/>
+      <c r="A49" s="92"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43"/>
       <c r="D49" s="43" t="s">
@@ -2640,7 +2701,7 @@
       <c r="L49" s="43"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="62"/>
+      <c r="A50" s="92"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>63</v>
@@ -2660,7 +2721,7 @@
       <c r="L50" s="43"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="62"/>
+      <c r="A51" s="92"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>63</v>
@@ -2680,7 +2741,7 @@
       <c r="L51" s="43"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="62"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>63</v>
@@ -2702,7 +2763,7 @@
       <c r="L52" s="43"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="62"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43" t="s">
         <v>63</v>
@@ -2726,7 +2787,7 @@
       <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="62"/>
+      <c r="A54" s="92"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43" t="s">
@@ -2746,7 +2807,7 @@
       <c r="L54" s="43"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="62"/>
+      <c r="A55" s="92"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43"/>
       <c r="D55" s="43" t="s">
@@ -2766,7 +2827,7 @@
       <c r="L55" s="43"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="62"/>
+      <c r="A56" s="92"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43"/>
       <c r="D56" s="43" t="s">
@@ -2788,7 +2849,7 @@
       <c r="L56" s="43"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="62"/>
+      <c r="A57" s="92"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43" t="s">
@@ -2812,7 +2873,7 @@
       <c r="L57" s="43"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="62"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="42"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
@@ -2830,7 +2891,7 @@
       <c r="L58" s="43"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="62"/>
+      <c r="A59" s="92"/>
       <c r="B59" s="42"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
@@ -2844,7 +2905,7 @@
       <c r="L59" s="43"/>
     </row>
     <row r="62" spans="1:12" ht="27">
-      <c r="A62" s="53" t="s">
+      <c r="A62" s="87" t="s">
         <v>74</v>
       </c>
       <c r="B62" s="42"/>
@@ -2861,7 +2922,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A63" s="53"/>
+      <c r="A63" s="87"/>
       <c r="B63" s="42" t="s">
         <v>75</v>
       </c>
@@ -2874,7 +2935,7 @@
       <c r="I63" s="43"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="53"/>
+      <c r="A64" s="87"/>
       <c r="B64" s="42" t="s">
         <v>76</v>
       </c>
@@ -2887,7 +2948,7 @@
       <c r="I64" s="43"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="53"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="42" t="s">
         <v>77</v>
       </c>
@@ -2900,7 +2961,7 @@
       <c r="I65" s="43"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="53"/>
+      <c r="A66" s="87"/>
       <c r="B66" s="42" t="s">
         <v>78</v>
       </c>
@@ -2913,7 +2974,7 @@
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="54"/>
+      <c r="A67" s="88"/>
       <c r="B67" s="42"/>
       <c r="C67" s="43"/>
       <c r="D67" s="43"/>
@@ -2924,7 +2985,7 @@
       <c r="I67" s="43"/>
     </row>
     <row r="70" spans="1:9" ht="27">
-      <c r="A70" s="53" t="s">
+      <c r="A70" s="87" t="s">
         <v>83</v>
       </c>
       <c r="B70" s="42"/>
@@ -2939,7 +3000,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="53"/>
+      <c r="A71" s="87"/>
       <c r="B71" s="42" t="s">
         <v>84</v>
       </c>
@@ -2951,8 +3012,8 @@
       <c r="H71" s="43"/>
       <c r="I71" s="43"/>
     </row>
-    <row r="72" spans="1:9" ht="27">
-      <c r="A72" s="53"/>
+    <row r="72" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A72" s="87"/>
       <c r="B72" s="42" t="s">
         <v>85</v>
       </c>
@@ -2965,7 +3026,7 @@
       <c r="I72" s="43"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="53"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="42" t="s">
         <v>86</v>
       </c>
@@ -2978,7 +3039,7 @@
       <c r="I73" s="43"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="53"/>
+      <c r="A74" s="87"/>
       <c r="B74" s="42" t="s">
         <v>87</v>
       </c>
@@ -2991,7 +3052,7 @@
       <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="54"/>
+      <c r="A75" s="88"/>
       <c r="B75" s="42" t="s">
         <v>116</v>
       </c>
@@ -3005,6 +3066,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="G4:I5"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="G8:I9"/>
+    <mergeCell ref="G10:I11"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="A36:A59"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="C18:E18"/>
@@ -3021,27 +3103,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="G4:I5"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="G8:I9"/>
-    <mergeCell ref="G10:I11"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A36:A59"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3103,10 +3164,10 @@
       <c r="C4" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="79"/>
+      <c r="G4" s="53"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
@@ -3115,12 +3176,12 @@
       <c r="C5" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3744,9 +3805,221 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="73.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="97" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A1" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="98" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A2" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A3" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A4" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A5" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A6" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A7" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A8" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A9" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A10" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A11" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A12" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A13" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A14" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A15" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A16" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="1" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A17" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="1" customFormat="1">
+      <c r="A18" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3789,7 +4062,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3805,12 +4078,12 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3841,17 +4114,17 @@
   <sheetData>
     <row r="1" spans="1:1" ht="40.5">
       <c r="A1" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="40.5">
       <c r="A2" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="40.5">
       <c r="A3" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
